--- a/scripts/tests/fixtures/overview/workbook-client-overview.xlsx
+++ b/scripts/tests/fixtures/overview/workbook-client-overview.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="89">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -230,6 +230,12 @@
     <t>0</t>
   </si>
   <si>
+    <t>Portfolios with no valuation on or before 2026-06-15</t>
+  </si>
+  <si>
+    <t>Portfolios with no valuation at the previous quarter end</t>
+  </si>
+  <si>
     <t>Tenant</t>
   </si>
   <si>
@@ -245,7 +251,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-15T08:00:00Z</t>
+    <t>2026-10-04T10:30:20Z</t>
   </si>
   <si>
     <t>Values are each portfolio's latest valuation on or before 2026-06-15, converted into CZK at that day's rate; a total that includes an amount with no rate is left empty, never converted at a guess.</t>
@@ -428,7 +434,9 @@
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="9"/>
+      <c r="B7" s="9" t="n">
+        <v>36750.0</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
@@ -863,7 +871,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.0"/>
@@ -965,38 +973,44 @@
         <v>71</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="3">
+      <c r="A18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="3">
         <v>33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -1037,6 +1051,16 @@
     <row r="28">
       <c r="A28" s="1" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/tests/fixtures/overview/workbook-client-overview.xlsx
+++ b/scripts/tests/fixtures/overview/workbook-client-overview.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="90">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -251,7 +251,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-10-04T10:30:20Z</t>
+    <t>2026-10-04T15:20:23Z</t>
   </si>
   <si>
     <t>Values are each portfolio's latest valuation on or before 2026-06-15, converted into CZK at that day's rate; a total that includes an amount with no rate is left empty, never converted at a guess.</t>
@@ -269,7 +269,10 @@
     <t>Cost basis: average (REPORT_COST_BASIS).</t>
   </si>
   <si>
-    <t>Income and fees: not available: the model carries no `fee`/`description`; fees, income and entry fees read 0, and entry fees stay inside withdrawals (IA-C49).</t>
+    <t>Income and fees: classified by income-labels.yaml v1 (14 labels); 1 of 9 cash and external-flow movements carry a label the table does not know, counted as other ('výplata na účet xy' ×1); 0 carry no label.</t>
+  </si>
+  <si>
+    <t>Security-leg fees in the window: 1040.00 CZK — the provider's record of the entry fees that arrive as their own withdrawals (classified fee above); not added to fees again.</t>
   </si>
   <si>
     <t>Amounts are in CZK, each converted at its own day's rate from investment.fx_rate (the ČNB fixing via cnb-rates, IA-C68) — the latest rate on or before that day; an amount with no rate is never converted at a guess.</t>
@@ -485,7 +488,7 @@
         <v>41</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>26871.67</v>
+        <v>13356.67</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>37</v>
@@ -501,7 +504,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>11.537484</v>
+        <v>5.734752</v>
       </c>
     </row>
     <row r="14">
@@ -651,7 +654,7 @@
         <v>3.629268</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>11.836111</v>
+        <v>5.834046</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>0.0</v>
@@ -794,10 +797,10 @@
         <v>28900.0</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>26651.67</v>
+        <v>13136.67</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>11.836111</v>
+        <v>5.834046</v>
       </c>
     </row>
     <row r="7">
@@ -858,10 +861,10 @@
         <v>35600.0</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>26871.67</v>
+        <v>13356.67</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>11.537484</v>
+        <v>5.734752</v>
       </c>
     </row>
   </sheetData>
@@ -871,7 +874,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.0"/>
@@ -1063,6 +1066,11 @@
         <v>88</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
